--- a/data/trans_orig/P21D2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención dental en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención dental en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35435</t>
+          <t>33242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63221</t>
+          <t>62800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>31257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57819</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90306</t>
+          <t>88201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79757</t>
+          <t>80939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110374</t>
+          <t>111236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78455</t>
+          <t>78858</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98695</t>
+          <t>99401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167937</t>
+          <t>168326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>204387</t>
+          <t>205578</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>42343</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78215</t>
+          <t>76085</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67871</t>
+          <t>68176</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93266</t>
+          <t>93126</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>118594</t>
+          <t>118181</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>160451</t>
+          <t>161834</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115988</t>
+          <t>117932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153926</t>
+          <t>153813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,47 +1427,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>55,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>143904</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>130274</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>157019</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>60,65%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>54,9%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>143904</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>129719</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>156816</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>60,65%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>54,67%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>257121</t>
+          <t>257801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302726</t>
+          <t>303239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,6%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32987</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>19731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47041</t>
+          <t>46627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63869</t>
+          <t>65171</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61197</t>
+          <t>61324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82154</t>
+          <t>82243</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114468</t>
+          <t>114111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140920</t>
+          <t>141612</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29874</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46433</t>
+          <t>46493</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58768</t>
+          <t>58572</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79543</t>
+          <t>79657</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>93559</t>
+          <t>92437</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>120530</t>
+          <t>120184</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1596</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1247</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46598</t>
+          <t>47135</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70803</t>
+          <t>72549</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>191216</t>
+          <t>186256</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100698</t>
+          <t>101958</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>260785</t>
+          <t>252841</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94779</t>
+          <t>94242</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>118234</t>
+          <t>117661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54473</t>
+          <t>59314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173122</t>
+          <t>171569</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127444</t>
+          <t>133942</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>285497</t>
+          <t>284163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -2663,97 +2663,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>2054</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2266</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>407</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>2238</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>2170</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>2267</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -2776,97 +2776,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1242</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2054</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1242</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4816</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3982</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1242</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4523</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40047</t>
+          <t>40075</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>53664</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26472</t>
+          <t>26741</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38696</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>69868</t>
+          <t>70484</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89742</t>
+          <t>90106</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28421</t>
+          <t>28864</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41895</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47746</t>
+          <t>47944</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66364</t>
+          <t>67232</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>768</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -3345,97 +3345,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>36250</t>
+          <t>35385</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55190</t>
+          <t>54916</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27473</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42657</t>
+          <t>43231</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>66536</t>
+          <t>67772</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>91467</t>
+          <t>93263</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63348</t>
+          <t>63438</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>82775</t>
+          <t>83373</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62452</t>
+          <t>62678</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>77880</t>
+          <t>78393</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>132633</t>
+          <t>130536</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>157937</t>
+          <t>156324</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,09%</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>345</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>17565</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>76781</t>
+          <t>76156</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>113641</t>
+          <t>113670</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>59378</t>
+          <t>59235</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>87886</t>
+          <t>88649</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>143309</t>
+          <t>143888</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>189717</t>
+          <t>190221</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>196792</t>
+          <t>196506</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>234285</t>
+          <t>234356</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>210679</t>
+          <t>210282</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>238666</t>
+          <t>239299</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>417074</t>
+          <t>418414</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>465228</t>
+          <t>465307</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -4370,97 +4370,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3487</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>794</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>3874</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>3190</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>68321</t>
+          <t>67362</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>375525</t>
+          <t>376530</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>193195</t>
+          <t>192857</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>226698</t>
+          <t>225448</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>187320</t>
+          <t>189453</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>577137</t>
+          <t>577884</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>175031</t>
+          <t>174601</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>484566</t>
+          <t>485873</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>112847</t>
+          <t>115621</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>144462</t>
+          <t>144940</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>309153</t>
+          <t>308589</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>712408</t>
+          <t>707360</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -4939,82 +4939,82 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>550</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>2762</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>29030</t>
+          <t>33364</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33143</t>
+          <t>31239</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>345485</t>
+          <t>362189</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>703127</t>
+          <t>704195</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>594684</t>
+          <t>593870</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>797464</t>
+          <t>795992</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>976637</t>
+          <t>968051</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1382742</t>
+          <t>1394349</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>915549</t>
+          <t>914460</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1296494</t>
+          <t>1277927</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>741058</t>
+          <t>743670</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>939514</t>
+          <t>937018</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1777611</t>
+          <t>1763700</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2223700</t>
+          <t>2215510</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>29596</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>39363</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>54867</t>
+          <t>54646</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>82350</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D2_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47976</t>
+          <t>49257</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33242</t>
+          <t>37748</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>63085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23565</t>
+          <t>26652</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31257</t>
+          <t>33940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>71541</t>
+          <t>75909</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55406</t>
+          <t>62574</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88201</t>
+          <t>90490</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96453</t>
+          <t>86383</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80939</t>
+          <t>72455</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111236</t>
+          <t>100304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91003</t>
+          <t>96103</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78858</t>
+          <t>86052</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99401</t>
+          <t>105003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>187456</t>
+          <t>182486</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168326</t>
+          <t>165262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>205578</t>
+          <t>198588</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>67,78%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>24290</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>34953</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59594</t>
+          <t>65325</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42343</t>
+          <t>50634</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76085</t>
+          <t>83020</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80036</t>
+          <t>85779</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68176</t>
+          <t>71754</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93126</t>
+          <t>100706</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>139631</t>
+          <t>151104</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>118181</t>
+          <t>130483</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>161834</t>
+          <t>173892</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>136187</t>
+          <t>140167</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117932</t>
+          <t>120829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153813</t>
+          <t>156611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>143904</t>
+          <t>152822</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130274</t>
+          <t>137747</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157019</t>
+          <t>167679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>280091</t>
+          <t>292989</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>257801</t>
+          <t>269155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>303239</t>
+          <t>313752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>66,13%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22708</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>14142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19731</t>
+          <t>24417</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>55767</t>
+          <t>54986</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46627</t>
+          <t>45934</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65171</t>
+          <t>63002</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>71799</t>
+          <t>70904</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61324</t>
+          <t>61348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82243</t>
+          <t>80573</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>127566</t>
+          <t>125890</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114111</t>
+          <t>113315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141612</t>
+          <t>138881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37451</t>
+          <t>36483</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46493</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68887</t>
+          <t>70621</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58572</t>
+          <t>61802</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79657</t>
+          <t>80280</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>106338</t>
+          <t>107105</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>92437</t>
+          <t>93962</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>120184</t>
+          <t>119820</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,05%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>53227</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23716</t>
+          <t>38255</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47135</t>
+          <t>71248</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>124407</t>
+          <t>65076</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72549</t>
+          <t>53515</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>186256</t>
+          <t>77421</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>157668</t>
+          <t>118303</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101958</t>
+          <t>99761</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>252841</t>
+          <t>140677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>108117</t>
+          <t>121233</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94242</t>
+          <t>103212</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117661</t>
+          <t>136205</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>120504</t>
+          <t>134709</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59314</t>
+          <t>122562</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>171569</t>
+          <t>146999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>228620</t>
+          <t>255942</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133942</t>
+          <t>233148</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>284163</t>
+          <t>274264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,95%</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>432</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47523</t>
+          <t>57943</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40075</t>
+          <t>50376</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53664</t>
+          <t>65337</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32621</t>
+          <t>38258</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26741</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38696</t>
+          <t>44767</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>80143</t>
+          <t>96201</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>70484</t>
+          <t>86071</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>90106</t>
+          <t>105732</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28864</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>36004</t>
+          <t>37962</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>31926</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>45241</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>57312</t>
+          <t>62551</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47944</t>
+          <t>52778</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67232</t>
+          <t>73486</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>805</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>44979</t>
+          <t>46905</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35385</t>
+          <t>37730</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>54916</t>
+          <t>56399</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>35069</t>
+          <t>36196</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>43231</t>
+          <t>44973</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>80048</t>
+          <t>83102</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>67772</t>
+          <t>71929</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93263</t>
+          <t>96008</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>73547</t>
+          <t>71750</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63438</t>
+          <t>62051</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>83373</t>
+          <t>81260</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>70451</t>
+          <t>71877</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62678</t>
+          <t>62717</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>78393</t>
+          <t>79765</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>143997</t>
+          <t>143627</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>130536</t>
+          <t>130687</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>156324</t>
+          <t>156149</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>751</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>776</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>377</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>93754</t>
+          <t>107943</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>76156</t>
+          <t>88971</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>113670</t>
+          <t>129093</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>72749</t>
+          <t>84164</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>59235</t>
+          <t>69212</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>88649</t>
+          <t>99544</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>166504</t>
+          <t>192107</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>143888</t>
+          <t>167398</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>190221</t>
+          <t>219908</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>216906</t>
+          <t>243766</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>196506</t>
+          <t>222576</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>234356</t>
+          <t>263063</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>225686</t>
+          <t>261560</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>210282</t>
+          <t>244868</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>239299</t>
+          <t>276350</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>442591</t>
+          <t>505326</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>418414</t>
+          <t>476137</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>465307</t>
+          <t>529878</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>74,91%</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>305195</t>
+          <t>354505</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>305195</t>
+          <t>354505</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>305195</t>
+          <t>354505</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>616931</t>
+          <t>707312</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>616931</t>
+          <t>707312</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>616931</t>
+          <t>707312</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>204817</t>
+          <t>240109</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>67362</t>
+          <t>217793</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>376530</t>
+          <t>257468</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>209685</t>
+          <t>252253</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>192857</t>
+          <t>234932</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>225448</t>
+          <t>270343</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>414501</t>
+          <t>492362</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>189453</t>
+          <t>465884</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>577884</t>
+          <t>518011</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>347299</t>
+          <t>118538</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>174601</t>
+          <t>100992</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>485873</t>
+          <t>141002</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>129045</t>
+          <t>149543</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>115621</t>
+          <t>133038</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>144940</t>
+          <t>166937</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>476343</t>
+          <t>268081</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>308589</t>
+          <t>243193</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>707360</t>
+          <t>295293</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>31239</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>587671</t>
+          <t>675695</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>362189</t>
+          <t>633137</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>704195</t>
+          <t>722066</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>649931</t>
+          <t>659282</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>593870</t>
+          <t>622682</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>795992</t>
+          <t>693736</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1237602</t>
+          <t>1334977</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>968051</t>
+          <t>1269431</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1394349</t>
+          <t>1394617</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1037267</t>
+          <t>842909</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>914460</t>
+          <t>794740</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1277927</t>
+          <t>887212</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>885482</t>
+          <t>975199</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>743670</t>
+          <t>940085</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>937018</t>
+          <t>1011149</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1922749</t>
+          <t>1818108</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1763700</t>
+          <t>1759740</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2215510</t>
+          <t>1878786</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>29596</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>54646</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>26281</t>
+          <t>30641</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>60451</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>84305</t>
+          <t>91886</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
